--- a/____EvoM1_TraitTable/locomotion.xlsx
+++ b/____EvoM1_TraitTable/locomotion.xlsx
@@ -4550,13 +4550,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4653BA9E-F977-499C-9F6F-F99BD16A0B93}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4EF97040-39E2-4AC8-9864-9E10AE1917E3}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF52ECB4-FC36-4BA1-9741-DB47A76A3A87}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A2A754A0-4474-4B26-A2A8-6CCDC8CA924C}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DF0E13FB-DD62-4E52-9C00-8D5EDD1457B4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{637611E3-9FC9-46FD-AC92-999FCC934C15}"/>
 </file>
--- a/____EvoM1_TraitTable/locomotion.xlsx
+++ b/____EvoM1_TraitTable/locomotion.xlsx
@@ -4550,13 +4550,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4EF97040-39E2-4AC8-9864-9E10AE1917E3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3C98FCA8-1DE8-4872-9A95-6682F383A4C8}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A2A754A0-4474-4B26-A2A8-6CCDC8CA924C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CEE29C78-5DB9-43A5-A62E-871C32CF7910}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{637611E3-9FC9-46FD-AC92-999FCC934C15}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D00A181E-E7CE-4BC8-94AD-ED5D7A2147CA}"/>
 </file>
--- a/____EvoM1_TraitTable/locomotion.xlsx
+++ b/____EvoM1_TraitTable/locomotion.xlsx
@@ -4550,13 +4550,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3C98FCA8-1DE8-4872-9A95-6682F383A4C8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FF27FACE-D6E5-466C-B4F6-30B561E6485B}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CEE29C78-5DB9-43A5-A62E-871C32CF7910}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2077F45A-1286-466D-A94A-8E54DD9EF848}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D00A181E-E7CE-4BC8-94AD-ED5D7A2147CA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D470C89C-EA04-488C-86CB-9C22D1D1F727}"/>
 </file>
--- a/____EvoM1_TraitTable/locomotion.xlsx
+++ b/____EvoM1_TraitTable/locomotion.xlsx
@@ -4541,22 +4541,22 @@
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
       <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FF27FACE-D6E5-466C-B4F6-30B561E6485B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{34BC512B-4E4A-4766-8085-611925FBDA10}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2077F45A-1286-466D-A94A-8E54DD9EF848}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5EF2E1E1-2A09-40D0-A89C-F6EA0B808CCC}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D470C89C-EA04-488C-86CB-9C22D1D1F727}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{338F8B0B-5EFF-4E10-B5D2-1FF54994AFCC}"/>
 </file>
--- a/____EvoM1_TraitTable/locomotion.xlsx
+++ b/____EvoM1_TraitTable/locomotion.xlsx
@@ -4550,13 +4550,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{34BC512B-4E4A-4766-8085-611925FBDA10}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{28422341-01DA-46B1-9DC9-587D7C4A0003}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5EF2E1E1-2A09-40D0-A89C-F6EA0B808CCC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DCD76A8B-B6CE-419B-9D5B-61244A4FB7CF}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{338F8B0B-5EFF-4E10-B5D2-1FF54994AFCC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{29815365-5614-4C68-85C9-C023D7D66D29}"/>
 </file>
--- a/____EvoM1_TraitTable/locomotion.xlsx
+++ b/____EvoM1_TraitTable/locomotion.xlsx
@@ -4541,22 +4541,22 @@
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
       <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FF27FACE-D6E5-466C-B4F6-30B561E6485B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EA58AB46-6A8C-4748-9B1F-C9530BB89D76}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2077F45A-1286-466D-A94A-8E54DD9EF848}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B1B7DA16-7FA3-4FF9-BC20-F9217277355B}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D470C89C-EA04-488C-86CB-9C22D1D1F727}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{213FD89B-F3F8-4966-AAB7-A1673C24D475}"/>
 </file>
--- a/____EvoM1_TraitTable/locomotion.xlsx
+++ b/____EvoM1_TraitTable/locomotion.xlsx
@@ -4550,13 +4550,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{28422341-01DA-46B1-9DC9-587D7C4A0003}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C44A89B8-4EB6-40A2-8FD2-34305F794E80}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DCD76A8B-B6CE-419B-9D5B-61244A4FB7CF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{54774759-9C25-42E3-9509-6BC676555500}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{29815365-5614-4C68-85C9-C023D7D66D29}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7A6B776E-775E-46F2-8C71-D8586E6D2D91}"/>
 </file>
--- a/____EvoM1_TraitTable/locomotion.xlsx
+++ b/____EvoM1_TraitTable/locomotion.xlsx
@@ -4550,13 +4550,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C44A89B8-4EB6-40A2-8FD2-34305F794E80}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0A9AC942-10C1-4ABA-ADED-5CE16CEA5D69}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{54774759-9C25-42E3-9509-6BC676555500}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{81B4B888-9E76-4ECF-9BF0-1855D0E28C29}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7A6B776E-775E-46F2-8C71-D8586E6D2D91}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{48995808-3427-4597-8F7D-D98B8F006ADB}"/>
 </file>
--- a/____EvoM1_TraitTable/locomotion.xlsx
+++ b/____EvoM1_TraitTable/locomotion.xlsx
@@ -4550,13 +4550,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0A9AC942-10C1-4ABA-ADED-5CE16CEA5D69}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{31D900BF-16E8-43AE-A4AA-15CDA7F5A287}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{81B4B888-9E76-4ECF-9BF0-1855D0E28C29}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B52B2EF8-460A-4B35-A076-F0EC4DDD5853}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{48995808-3427-4597-8F7D-D98B8F006ADB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1209A94C-7FAF-4991-AFB8-2D76C64E2353}"/>
 </file>
--- a/____EvoM1_TraitTable/locomotion.xlsx
+++ b/____EvoM1_TraitTable/locomotion.xlsx
@@ -4550,13 +4550,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{31D900BF-16E8-43AE-A4AA-15CDA7F5A287}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3F2AE094-4963-4711-A831-5CAB1B78BEB7}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B52B2EF8-460A-4B35-A076-F0EC4DDD5853}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{321CDF18-FFB7-430B-967B-05AF91718A0F}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1209A94C-7FAF-4991-AFB8-2D76C64E2353}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{83195DD9-8C02-49A0-89F3-B03E241252CC}"/>
 </file>
--- a/____EvoM1_TraitTable/locomotion.xlsx
+++ b/____EvoM1_TraitTable/locomotion.xlsx
@@ -4550,13 +4550,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3F2AE094-4963-4711-A831-5CAB1B78BEB7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1D9F7B28-A002-4627-9079-DDD5B3CAE151}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{321CDF18-FFB7-430B-967B-05AF91718A0F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E63EFFB8-C6C1-40B4-87E9-3A1076D64E60}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{83195DD9-8C02-49A0-89F3-B03E241252CC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FD208A5C-88B3-4775-8DA8-34340F4C9249}"/>
 </file>
--- a/____EvoM1_TraitTable/locomotion.xlsx
+++ b/____EvoM1_TraitTable/locomotion.xlsx
@@ -4550,13 +4550,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1D9F7B28-A002-4627-9079-DDD5B3CAE151}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E7C04834-9D4C-45C4-983C-2B37A346DD7C}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E63EFFB8-C6C1-40B4-87E9-3A1076D64E60}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BA38A677-3BF4-4372-9725-A6B74A92AB43}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FD208A5C-88B3-4775-8DA8-34340F4C9249}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B182C045-9367-4047-B650-ABB62155E4E0}"/>
 </file>
--- a/____EvoM1_TraitTable/locomotion.xlsx
+++ b/____EvoM1_TraitTable/locomotion.xlsx
@@ -4550,13 +4550,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E7C04834-9D4C-45C4-983C-2B37A346DD7C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC726587-B583-4E0F-8560-F2FD1DE5C3D2}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BA38A677-3BF4-4372-9725-A6B74A92AB43}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A8E4F0F4-FE8F-4B28-A737-09BEAFE69AB4}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B182C045-9367-4047-B650-ABB62155E4E0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D1CF9A9F-575C-44A2-8DE0-715F08061D06}"/>
 </file>
--- a/____EvoM1_TraitTable/locomotion.xlsx
+++ b/____EvoM1_TraitTable/locomotion.xlsx
@@ -4550,13 +4550,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC726587-B583-4E0F-8560-F2FD1DE5C3D2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{051F17A2-CB0C-4E4F-B021-82A5B51D5E9B}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A8E4F0F4-FE8F-4B28-A737-09BEAFE69AB4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12FDA20A-94E5-4FDF-949A-33C143BB94E0}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D1CF9A9F-575C-44A2-8DE0-715F08061D06}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EF1AAD52-7ACE-497A-851D-E5D201E4693B}"/>
 </file>
--- a/____EvoM1_TraitTable/locomotion.xlsx
+++ b/____EvoM1_TraitTable/locomotion.xlsx
@@ -4550,13 +4550,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{051F17A2-CB0C-4E4F-B021-82A5B51D5E9B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A8907309-23A9-4482-A7AF-21231D52B393}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12FDA20A-94E5-4FDF-949A-33C143BB94E0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CDEDCFC4-5439-4BDC-8220-AAF29376C9FC}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EF1AAD52-7ACE-497A-851D-E5D201E4693B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E6E4CF08-E40C-4BF9-AB35-E117CF5349B2}"/>
 </file>
--- a/____EvoM1_TraitTable/locomotion.xlsx
+++ b/____EvoM1_TraitTable/locomotion.xlsx
@@ -4550,13 +4550,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A8907309-23A9-4482-A7AF-21231D52B393}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7B20FC1-FAE7-44E6-9D77-5C22B834C5EB}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CDEDCFC4-5439-4BDC-8220-AAF29376C9FC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{02EBFEE6-65DE-4144-9EDD-9F4EBDD2F171}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E6E4CF08-E40C-4BF9-AB35-E117CF5349B2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{617E4A32-68D7-4E36-8FF4-0E390A2E61A9}"/>
 </file>
--- a/____EvoM1_TraitTable/locomotion.xlsx
+++ b/____EvoM1_TraitTable/locomotion.xlsx
@@ -4550,13 +4550,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7B20FC1-FAE7-44E6-9D77-5C22B834C5EB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A3CA73B2-7C4B-4319-880C-2321B0E3A93C}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{02EBFEE6-65DE-4144-9EDD-9F4EBDD2F171}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{61156140-4D09-4B7B-AD63-16049B929C5F}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{617E4A32-68D7-4E36-8FF4-0E390A2E61A9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{76CB5E51-43E9-4B0A-A4ED-1DB94EB22097}"/>
 </file>
--- a/____EvoM1_TraitTable/locomotion.xlsx
+++ b/____EvoM1_TraitTable/locomotion.xlsx
@@ -4550,13 +4550,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A3CA73B2-7C4B-4319-880C-2321B0E3A93C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{337E9378-3E09-4908-9DD8-2E78EB0B5103}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{61156140-4D09-4B7B-AD63-16049B929C5F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3451DD71-BF94-4D88-9897-9A28F6B390CB}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{76CB5E51-43E9-4B0A-A4ED-1DB94EB22097}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{88021BEE-E2D6-4734-AC85-FB1D4FCFBD72}"/>
 </file>
--- a/____EvoM1_TraitTable/locomotion.xlsx
+++ b/____EvoM1_TraitTable/locomotion.xlsx
@@ -4550,13 +4550,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{337E9378-3E09-4908-9DD8-2E78EB0B5103}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B64CF67E-CE55-4CEB-AAE0-B668E49C35B5}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3451DD71-BF94-4D88-9897-9A28F6B390CB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{11B16CEB-024C-4F26-BEB1-42C410E88A2A}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{88021BEE-E2D6-4734-AC85-FB1D4FCFBD72}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{28EC3596-0A4E-4EA5-BFC7-C74FA7B3BDF9}"/>
 </file>
--- a/____EvoM1_TraitTable/locomotion.xlsx
+++ b/____EvoM1_TraitTable/locomotion.xlsx
@@ -4550,13 +4550,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B64CF67E-CE55-4CEB-AAE0-B668E49C35B5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{76F362A8-29A6-40C4-A3BA-150A5DB2BB54}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{11B16CEB-024C-4F26-BEB1-42C410E88A2A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7B6FB463-284F-40B2-9EBF-A3C9AA035CB8}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{28EC3596-0A4E-4EA5-BFC7-C74FA7B3BDF9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CC145E14-5724-4995-9591-55DB93EABA1E}"/>
 </file>
--- a/____EvoM1_TraitTable/locomotion.xlsx
+++ b/____EvoM1_TraitTable/locomotion.xlsx
@@ -4550,13 +4550,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{76F362A8-29A6-40C4-A3BA-150A5DB2BB54}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A57ECBEA-5D56-4E8E-BFBA-642EC944047E}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7B6FB463-284F-40B2-9EBF-A3C9AA035CB8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DC267119-CF24-44AF-B58E-67A63C7C0FDF}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CC145E14-5724-4995-9591-55DB93EABA1E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F7C96887-0A63-4EF8-AFAF-3E01C25EAED3}"/>
 </file>
--- a/____EvoM1_TraitTable/locomotion.xlsx
+++ b/____EvoM1_TraitTable/locomotion.xlsx
@@ -4550,13 +4550,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A57ECBEA-5D56-4E8E-BFBA-642EC944047E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5DF4EB92-12BB-4F09-A64B-DAF2B3DFD768}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DC267119-CF24-44AF-B58E-67A63C7C0FDF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{652C0235-420E-473C-8D44-E98F781F8961}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F7C96887-0A63-4EF8-AFAF-3E01C25EAED3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{11322335-54EC-4406-82A0-C184304A57E8}"/>
 </file>
--- a/____EvoM1_TraitTable/locomotion.xlsx
+++ b/____EvoM1_TraitTable/locomotion.xlsx
@@ -4550,13 +4550,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5DF4EB92-12BB-4F09-A64B-DAF2B3DFD768}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6CACC9D1-447D-423C-8CA0-6EF9CCDB2FF9}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{652C0235-420E-473C-8D44-E98F781F8961}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4B207409-D8EB-48CB-A875-BFDCAE2573D3}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{11322335-54EC-4406-82A0-C184304A57E8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{579E12BF-BC59-4B53-848D-30E12615D787}"/>
 </file>
--- a/____EvoM1_TraitTable/locomotion.xlsx
+++ b/____EvoM1_TraitTable/locomotion.xlsx
@@ -4550,13 +4550,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6CACC9D1-447D-423C-8CA0-6EF9CCDB2FF9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{05AA3777-DFFF-4769-964D-805E5ED6F012}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4B207409-D8EB-48CB-A875-BFDCAE2573D3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{719BF742-1C0B-4267-BA41-3D07A8D30A52}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{579E12BF-BC59-4B53-848D-30E12615D787}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3B213E19-6FB1-4729-8369-4E2715A6FE0E}"/>
 </file>
--- a/____EvoM1_TraitTable/locomotion.xlsx
+++ b/____EvoM1_TraitTable/locomotion.xlsx
@@ -4550,13 +4550,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{05AA3777-DFFF-4769-964D-805E5ED6F012}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A4B1180B-4692-4A56-B36F-AF68CF7CF525}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{719BF742-1C0B-4267-BA41-3D07A8D30A52}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E58EC66C-D028-4AB5-97F0-5944C6EB6ADE}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3B213E19-6FB1-4729-8369-4E2715A6FE0E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B23ED938-AA59-4F89-BA45-33F0B8609532}"/>
 </file>
--- a/____EvoM1_TraitTable/locomotion.xlsx
+++ b/____EvoM1_TraitTable/locomotion.xlsx
@@ -4550,13 +4550,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A4B1180B-4692-4A56-B36F-AF68CF7CF525}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C087C66-4E31-4C1F-9477-24FD903016D7}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E58EC66C-D028-4AB5-97F0-5944C6EB6ADE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5C6AD0C6-193F-4883-AE9A-28DAC7243C43}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B23ED938-AA59-4F89-BA45-33F0B8609532}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA5FD2F9-BFF1-4E86-B301-D0CCC89DD13D}"/>
 </file>